--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -286,7 +286,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="9">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -296,37 +296,23 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <b/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
-      <b/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
+      <i/>
       <sz val="8"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <i/>
     </font>
   </fonts>
   <fills count="3">
@@ -339,10 +325,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -352,171 +339,125 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,19 +479,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -558,16 +499,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -578,13 +519,13 @@
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -595,13 +536,13 @@
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -609,16 +550,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
@@ -626,7 +567,7 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -643,16 +584,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="20" t="s">
+      <c r="C7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -678,19 +619,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -698,16 +639,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -718,13 +659,13 @@
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -735,13 +676,13 @@
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -749,16 +690,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
@@ -766,7 +707,7 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -783,16 +724,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="C7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -800,21 +741,21 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="20" t="s">
+      <c r="C8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="0"/>
@@ -846,22 +787,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -869,19 +810,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -892,16 +833,16 @@
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="6" t="s">
         <v>45</v>
       </c>
     </row>
@@ -909,19 +850,19 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="16" t="s">
         <v>45</v>
       </c>
     </row>
@@ -929,19 +870,19 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="9" t="s">
         <v>46</v>
       </c>
     </row>
@@ -949,19 +890,19 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="27" t="s">
+      <c r="C6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>1</v>
       </c>
     </row>
@@ -969,24 +910,24 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="29" t="s">
+      <c r="C7" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C8" s="0"/>
@@ -1017,19 +958,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1037,16 +978,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1057,13 +998,13 @@
       <c r="B3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1071,16 +1012,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="16" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1091,13 +1032,13 @@
       <c r="B5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1105,16 +1046,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="22" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1122,7 +1063,7 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -1139,16 +1080,16 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="20" t="s">
+      <c r="C8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1174,19 +1115,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1194,16 +1135,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1214,13 +1155,13 @@
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1231,13 +1172,13 @@
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1245,16 +1186,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1262,7 +1203,7 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1279,21 +1220,21 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="20" t="s">
+      <c r="C7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="0"/>
@@ -1323,19 +1264,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1343,16 +1284,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1363,13 +1304,13 @@
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1380,13 +1321,13 @@
       <c r="B4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1394,16 +1335,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="9" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1411,7 +1352,7 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="23" t="s">
         <v>75</v>
       </c>
       <c r="C6" s="9" t="s">
@@ -1425,7 +1366,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="13" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="0"/>
@@ -1454,109 +1395,109 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="31" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="A2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="30" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="28" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="28" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="29" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="C6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="29" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="0"/>

--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -329,7 +329,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -339,10 +339,38 @@
     </border>
     <border/>
     <border>
-      <left/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
       <right/>
       <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -354,16 +382,58 @@
     </border>
     <border>
       <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin"/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -373,24 +443,45 @@
       <alignment horizontal="general" vertical="bottom" wrapText="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center" wrapText="false"/>
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="false"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="false"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -402,34 +493,46 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="false"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center" wrapText="false"/>
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="general" vertical="bottom" wrapText="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="false"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -441,16 +544,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -479,19 +597,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -499,16 +617,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="16" t="s">
         <v>5</v>
       </c>
     </row>
@@ -516,16 +634,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -533,16 +651,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -550,16 +668,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="14" t="s">
         <v>18</v>
       </c>
     </row>
@@ -567,16 +685,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="C6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -584,16 +702,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="C7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -619,19 +737,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -639,16 +757,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="16" t="s">
         <v>5</v>
       </c>
     </row>
@@ -656,16 +774,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -673,16 +791,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -690,16 +808,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="14" t="s">
         <v>18</v>
       </c>
     </row>
@@ -707,16 +825,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="C6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -724,16 +842,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="C7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -741,21 +859,21 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="C8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="20" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="0"/>
@@ -787,22 +905,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="11" t="s">
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -810,19 +928,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="16" t="s">
         <v>5</v>
       </c>
     </row>
@@ -830,19 +948,19 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -850,19 +968,19 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="24" t="s">
         <v>45</v>
       </c>
     </row>
@@ -870,19 +988,19 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="14" t="s">
         <v>46</v>
       </c>
     </row>
@@ -890,19 +1008,19 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="20" t="s">
+      <c r="C6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="30" t="s">
         <v>1</v>
       </c>
     </row>
@@ -910,24 +1028,24 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="19" t="s">
+      <c r="C7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="20" t="s">
         <v>47</v>
       </c>
       <c r="C8" s="0"/>
@@ -958,19 +1076,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -978,16 +1096,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="16" t="s">
         <v>5</v>
       </c>
     </row>
@@ -995,16 +1113,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1012,16 +1130,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="24" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1029,16 +1147,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="8" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1046,16 +1164,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="33" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1063,16 +1181,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="C7" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1080,16 +1198,16 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="C8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1115,19 +1233,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1135,16 +1253,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="16" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1152,16 +1270,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1169,16 +1287,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1186,16 +1304,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="14" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1203,16 +1321,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="C6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1220,21 +1338,21 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="C7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="20" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="0"/>
@@ -1264,19 +1382,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1284,16 +1402,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="16" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1301,16 +1419,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1318,16 +1436,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1335,16 +1453,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="14" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1352,21 +1470,21 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="C6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="20" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="0"/>
@@ -1395,109 +1513,109 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="31" t="s">
+      <c r="B1" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="47" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30" t="s">
+      <c r="A2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="45" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="25" t="s">
+      <c r="A3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="41" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="25" t="s">
+      <c r="A4" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="41" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="26" t="s">
+      <c r="A5" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="43" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="27" t="s">
+      <c r="A6" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="29" t="s">
+      <c r="C6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="43" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="35" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="0"/>

--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -13,13 +13,14 @@
     <sheet name="Cross-Tab Row Pct" sheetId="5" r:id="rId7"/>
     <sheet name="Small Cells Primary" sheetId="6" r:id="rId8"/>
     <sheet name="Small Cells Complement" sheetId="7" r:id="rId9"/>
+    <sheet name="Small Cells Primary Mode" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="257" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="288" uniqueCount="92">
   <si>
     <t>Table 16. Treatment by Sex</t>
   </si>
@@ -39,19 +40,19 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Fisher's exact test: p = 0.812</t>
-  </si>
-  <si>
-    <t>OR = 1.0 (95% CI: 0.9, 1.1)</t>
+    <t>Fisher's exact test: p &lt; 0.001</t>
+  </si>
+  <si>
+    <t>OR = 0.8 (95% CI: 0.8, 0.9)</t>
   </si>
   <si>
     <t>Male</t>
   </si>
   <si>
-    <t>3,583 (59.4%)</t>
-  </si>
-  <si>
-    <t>2,445 (40.6%)</t>
+    <t>3,399 (56.4%)</t>
+  </si>
+  <si>
+    <t>2,629 (43.6%)</t>
   </si>
   <si>
     <t>6,028</t>
@@ -60,19 +61,19 @@
     <t>Female</t>
   </si>
   <si>
-    <t>5,351 (59.6%)</t>
-  </si>
-  <si>
-    <t>3,621 (40.4%)</t>
+    <t>5,530 (61.6%)</t>
+  </si>
+  <si>
+    <t>3,442 (38.4%)</t>
   </si>
   <si>
     <t>8,972</t>
   </si>
   <si>
-    <t>8,934</t>
-  </si>
-  <si>
-    <t>6,066</t>
+    <t>8,929</t>
+  </si>
+  <si>
+    <t>6,071</t>
   </si>
   <si>
     <t>15,000</t>
@@ -81,22 +82,22 @@
     <t>Table 16a. Treatment-Outcome Association Measures</t>
   </si>
   <si>
-    <t>Pearson's chi-squared test: chi2 = 0.84, p = 0.359</t>
-  </si>
-  <si>
-    <t>RR = 1.0 (95% CI: 1.0, 1.1)</t>
-  </si>
-  <si>
-    <t>RD = 0.008 (95% CI: -0.009, 0.024)</t>
+    <t>Pearson's chi-squared test: chi2 = 8.29, p = 0.004</t>
+  </si>
+  <si>
+    <t>RR = 1.1 (95% CI: 1.0, 1.1)</t>
+  </si>
+  <si>
+    <t>RD = 0.024 (95% CI: 0.008, 0.041)</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>5,834 (59.8%)</t>
-  </si>
-  <si>
-    <t>3,917 (40.2%)</t>
+    <t>5,887 (60.4%)</t>
+  </si>
+  <si>
+    <t>3,864 (39.6%)</t>
   </si>
   <si>
     <t>9,751</t>
@@ -105,10 +106,10 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>3,100 (59.1%)</t>
-  </si>
-  <si>
-    <t>2,149 (40.9%)</t>
+    <t>3,042 (58.0%)</t>
+  </si>
+  <si>
+    <t>2,207 (42.0%)</t>
   </si>
   <si>
     <t>5,249</t>
@@ -216,19 +217,19 @@
     <t>Table 16d. Treatment-Outcome (Row Percentages)</t>
   </si>
   <si>
-    <t>OR = 1.0 (95% CI: 1.0, 1.1)</t>
-  </si>
-  <si>
-    <t>5,834 (65.3%)</t>
-  </si>
-  <si>
-    <t>3,917 (64.6%)</t>
-  </si>
-  <si>
-    <t>3,100 (34.7%)</t>
-  </si>
-  <si>
-    <t>2,149 (35.4%)</t>
+    <t>OR = 1.1 (95% CI: 1.0, 1.2)</t>
+  </si>
+  <si>
+    <t>5,887 (65.9%)</t>
+  </si>
+  <si>
+    <t>3,864 (63.6%)</t>
+  </si>
+  <si>
+    <t>3,042 (34.1%)</t>
+  </si>
+  <si>
+    <t>2,207 (36.4%)</t>
   </si>
   <si>
     <t>Percentages are row percentages within each treatment group.</t>
@@ -280,6 +281,21 @@
   </si>
   <si>
     <t>20</t>
+  </si>
+  <si>
+    <t>Small-cell suppression: primary mode</t>
+  </si>
+  <si>
+    <t>Fisher's exact test: p = 0.170</t>
+  </si>
+  <si>
+    <t>6 (75.0%)</t>
+  </si>
+  <si>
+    <t>8 (66.7%)</t>
+  </si>
+  <si>
+    <t>Counts from 1 to 4 are shown as &lt;5 without a percentage (primary suppression only: no complementary cells are masked, and totals and tests are shown as computed). This protects printed counts only.</t>
   </si>
 </sst>
 </file>
@@ -1513,8 +1529,139 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
       <c r="A1" s="48" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B1" s="47" t="s">
         <v>1</v>
@@ -1557,7 +1704,7 @@
         <v>77</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E3" s="41" t="s">
         <v>80</v>
@@ -1571,7 +1718,7 @@
         <v>74</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D4" s="40" t="s">
         <v>77</v>
@@ -1602,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C6" s="42" t="s">
         <v>1</v>
@@ -1616,7 +1763,7 @@
     </row>
     <row r="7">
       <c r="B7" s="35" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>

--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -295,7 +295,7 @@
     <t>8 (66.7%)</t>
   </si>
   <si>
-    <t>Counts from 1 to 4 are shown as &lt;5 without a percentage (primary suppression only: no complementary cells are masked, and totals and tests are shown as computed). This protects printed counts only.</t>
+    <t>Counts from 1 to 4 are shown as &lt;5 without a percentage (primary suppression only: no complementary cells are masked). This protects printed counts only.</t>
   </si>
 </sst>
 </file>

--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -133,7 +133,7 @@
     <t>Pearson's chi-squared test: chi2 = 26.67, p &lt; 0.001</t>
   </si>
   <si>
-    <t>P for trend = &lt;0.001</t>
+    <t>P for trend &lt; 0.001</t>
   </si>
   <si>
     <t>Low</t>
@@ -181,10 +181,10 @@
     <t>Tertiary</t>
   </si>
   <si>
-    <t>Pearson's chi-squared test: chi2 = 1.75, p = 0.418</t>
-  </si>
-  <si>
-    <t>P for trend = 0.288</t>
+    <t>Pearson's chi-squared test: chi2 = 1.75, p = 0.42</t>
+  </si>
+  <si>
+    <t>P for trend = 0.29</t>
   </si>
   <si>
     <t>2,543 (26.1%)</t>
@@ -286,7 +286,7 @@
     <t>Small-cell suppression: primary mode</t>
   </si>
   <si>
-    <t>Fisher's exact test: p = 0.170</t>
+    <t>Fisher's exact test: p = 0.17</t>
   </si>
   <si>
     <t>6 (75.0%)</t>

--- a/tabtools/demo/demo_crosstab.xlsx
+++ b/tabtools/demo/demo_crosstab.xlsx
@@ -43,16 +43,16 @@
     <t>Fisher's exact test: p &lt; 0.001</t>
   </si>
   <si>
-    <t>OR = 0.8 (95% CI: 0.8, 0.9)</t>
+    <t>OR = 0.80 (95% CI: 0.75, 0.86)</t>
   </si>
   <si>
     <t>Male</t>
   </si>
   <si>
-    <t>3,399 (56.4%)</t>
-  </si>
-  <si>
-    <t>2,629 (43.6%)</t>
+    <t>3,399 (56.39%)</t>
+  </si>
+  <si>
+    <t>2,629 (43.61%)</t>
   </si>
   <si>
     <t>6,028</t>
@@ -61,10 +61,10 @@
     <t>Female</t>
   </si>
   <si>
-    <t>5,530 (61.6%)</t>
-  </si>
-  <si>
-    <t>3,442 (38.4%)</t>
+    <t>5,530 (61.64%)</t>
+  </si>
+  <si>
+    <t>3,442 (38.36%)</t>
   </si>
   <si>
     <t>8,972</t>
@@ -85,19 +85,19 @@
     <t>Pearson's chi-squared test: chi2 = 8.29, p = 0.004</t>
   </si>
   <si>
-    <t>RR = 1.1 (95% CI: 1.0, 1.1)</t>
-  </si>
-  <si>
-    <t>RD = 0.024 (95% CI: 0.008, 0.041)</t>
+    <t>RR = 1.06 (95% CI: 1.02, 1.10)</t>
+  </si>
+  <si>
+    <t>RD = 0.0242 (95% CI: 0.0077, 0.0407)</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>5,887 (60.4%)</t>
-  </si>
-  <si>
-    <t>3,864 (39.6%)</t>
+    <t>5,887 (60.37%)</t>
+  </si>
+  <si>
+    <t>3,864 (39.63%)</t>
   </si>
   <si>
     <t>9,751</t>
@@ -106,10 +106,10 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>3,042 (58.0%)</t>
-  </si>
-  <si>
-    <t>2,207 (42.0%)</t>
+    <t>3,042 (57.95%)</t>
+  </si>
+  <si>
+    <t>2,207 (42.05%)</t>
   </si>
   <si>
     <t>5,249</t>
@@ -217,19 +217,19 @@
     <t>Table 16d. Treatment-Outcome (Row Percentages)</t>
   </si>
   <si>
-    <t>OR = 1.1 (95% CI: 1.0, 1.2)</t>
-  </si>
-  <si>
-    <t>5,887 (65.9%)</t>
-  </si>
-  <si>
-    <t>3,864 (63.6%)</t>
-  </si>
-  <si>
-    <t>3,042 (34.1%)</t>
-  </si>
-  <si>
-    <t>2,207 (36.4%)</t>
+    <t>OR = 1.11 (95% CI: 1.03, 1.18)</t>
+  </si>
+  <si>
+    <t>5,887 (65.93%)</t>
+  </si>
+  <si>
+    <t>3,864 (63.65%)</t>
+  </si>
+  <si>
+    <t>3,042 (34.07%)</t>
+  </si>
+  <si>
+    <t>2,207 (36.35%)</t>
   </si>
   <si>
     <t>Percentages are row percentages within each treatment group.</t>
